--- a/business_surveys/049_curriculum_relevance_for_future_skills_survey--business_surveys.xlsx
+++ b/business_surveys/049_curriculum_relevance_for_future_skills_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'ceo'}</t>
+          <t>ceo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'CEO'}</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cto'}</t>
+          <t>cto</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'CTO'}</t>
+          <t>CTO</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'software_engineer'}</t>
+          <t>software_engineer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Software Engineer'}</t>
+          <t>Software Engineer</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'project_manager'}</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Project Manager'}</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'yes,_i_have_access'}</t>
+          <t>yes,_i_have_access</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Yes, I have access'}</t>
+          <t>Yes, I have access</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'no,_but_i_wish_i_had_access'}</t>
+          <t>no,_but_i_wish_i_had_access</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'No, but I wish I had access'}</t>
+          <t>No, but I wish I had access</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_"no,_and_i_don't_need_access"}</t>
+          <t>no,_and_i_don't_need_access</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': "No, and I don't need access"}</t>
+          <t>No, and I don't need access</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_relevant'}</t>
+          <t>very_relevant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very relevant'}</t>
+          <t>Very relevant</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_relevant'}</t>
+          <t>somewhat_relevant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat relevant'}</t>
+          <t>Somewhat relevant</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very_relevant'}</t>
+          <t>not_very_relevant</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very relevant'}</t>
+          <t>Not very relevant</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all_relevant'}</t>
+          <t>not_at_all_relevant</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all relevant'}</t>
+          <t>Not at all relevant</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'practical_application'}</t>
+          <t>practical_application</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Practical application'}</t>
+          <t>Practical application</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'theoretical_foundation'}</t>
+          <t>theoretical_foundation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Theoretical foundation'}</t>
+          <t>Theoretical foundation</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'career_advancement'}</t>
+          <t>career_advancement</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Career advancement'}</t>
+          <t>Career advancement</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'networking_opportunities'}</t>
+          <t>networking_opportunities</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Networking opportunities'}</t>
+          <t>Networking opportunities</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very likely'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat likely'}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very_likely'}</t>
+          <t>not_very_likely</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not very likely'}</t>
+          <t>Not very likely</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not at all likely'}</t>
+          <t>Not at all likely</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'add_more_practical_training_activities'}</t>
+          <t>add_more_practical_training_activities</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Add more practical training activities'}</t>
+          <t>Add more practical training activities</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'increase_the_frequency_of_training_sessions'}</t>
+          <t>increase_the_frequency_of_training_sessions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Increase the frequency of training sessions'}</t>
+          <t>Increase the frequency of training sessions</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in-person_meetings'}</t>
+          <t>in-person_meetings</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In-person meetings'}</t>
+          <t>In-person meetings</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'online_meetings'}</t>
+          <t>online_meetings</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Online meetings'}</t>
+          <t>Online meetings</t>
         </is>
       </c>
     </row>
